--- a/docs/詳細設計書/●共通設計書_ログ.xlsx
+++ b/docs/詳細設計書/●共通設計書_ログ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\詳細設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2518481C-30B7-4F0D-836D-58D16A3CF44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED946D46-FA50-4744-9E1B-78FA55B88457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13095" yWindow="-16395" windowWidth="29040" windowHeight="15720" xr2:uid="{8ACC595D-EFF6-4B0D-A72B-D80AA8D4CEF2}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="67">
   <si>
     <t>Javaのログライブラリ:Logback</t>
     <phoneticPr fontId="2"/>
@@ -346,7 +346,79 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ログにオンコード</t>
+    <t>1.4.1　ログにオンコードする項目</t>
+    <rPh sb="16" eb="18">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.4.2　constから取得する項目</t>
+    <rPh sb="12" eb="14">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IPアドレス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理対象</t>
+    <rPh sb="0" eb="4">
+      <t>ショリタイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理結果</t>
+    <rPh sb="0" eb="4">
+      <t>ショリケッカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エラー内容</t>
+    <rPh sb="3" eb="5">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ログレベル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>処理内容</t>
+    <rPh sb="0" eb="4">
+      <t>ショリナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>＊項目の詳細は1.1.1ログ出力フォーマット参照</t>
+  </si>
+  <si>
+    <t>＊項目の詳細は1.1.1ログ出力フォーマット参照</t>
+    <rPh sb="1" eb="3">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サンショウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -600,7 +672,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -685,6 +757,111 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -694,100 +871,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
@@ -807,15 +897,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1131,241 +1212,241 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA031CC-9F73-4D89-B850-54BF76287348}">
-  <dimension ref="A1:AO74"/>
+  <dimension ref="A1:AO78"/>
   <sheetFormatPr defaultColWidth="3.7265625" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="3.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="49" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="50" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="49" t="s">
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="53" t="s">
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="49" t="s">
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="54">
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="39">
         <v>45566</v>
       </c>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
     </row>
     <row r="2" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="49" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="50" t="s">
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="40"/>
+      <c r="AM2" s="40"/>
+      <c r="AN2" s="40"/>
+      <c r="AO2" s="40"/>
     </row>
     <row r="3" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="49" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="53" t="s">
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="49" t="s">
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="53" t="s">
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="49" t="s">
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
-      <c r="AL3" s="54">
+      <c r="AJ3" s="37"/>
+      <c r="AK3" s="37"/>
+      <c r="AL3" s="39">
         <v>45614</v>
       </c>
-      <c r="AM3" s="55"/>
-      <c r="AN3" s="55"/>
-      <c r="AO3" s="55"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="40"/>
     </row>
     <row r="4" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="49" t="s">
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="53" t="s">
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="53"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="53"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="53"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="53"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="53"/>
-      <c r="AH4" s="53"/>
-      <c r="AI4" s="49"/>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
-      <c r="AL4" s="55"/>
-      <c r="AM4" s="55"/>
-      <c r="AN4" s="55"/>
-      <c r="AO4" s="55"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="37"/>
+      <c r="AC4" s="37"/>
+      <c r="AD4" s="37"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="37"/>
+      <c r="AJ4" s="37"/>
+      <c r="AK4" s="37"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
     </row>
     <row r="5" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="56" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="57"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="34" t="s">
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="59" t="s">
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
       <c r="O5" s="18"/>
       <c r="P5" s="18"/>
       <c r="Q5" s="18"/>
@@ -1404,32 +1485,32 @@
       <c r="E6" s="33"/>
       <c r="F6" s="33"/>
       <c r="G6" s="33"/>
-      <c r="H6" s="60" t="s">
+      <c r="H6" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="61"/>
-      <c r="W6" s="61"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="61"/>
-      <c r="Z6" s="61"/>
-      <c r="AA6" s="61"/>
-      <c r="AB6" s="61"/>
-      <c r="AC6" s="61"/>
-      <c r="AD6" s="61"/>
-      <c r="AE6" s="62"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="35"/>
+      <c r="AC6" s="35"/>
+      <c r="AD6" s="35"/>
+      <c r="AE6" s="36"/>
       <c r="AF6" s="33" t="s">
         <v>30</v>
       </c>
@@ -1439,20 +1520,20 @@
       <c r="AJ6" s="33"/>
       <c r="AK6" s="33"/>
       <c r="AL6" s="33"/>
-      <c r="AM6" s="34" t="s">
+      <c r="AM6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="AN6" s="34"/>
-      <c r="AO6" s="34"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
     </row>
     <row r="7" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A7" s="35"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
       <c r="H7" s="17"/>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
@@ -1477,25 +1558,25 @@
       <c r="AC7" s="16"/>
       <c r="AD7" s="16"/>
       <c r="AE7" s="16"/>
-      <c r="AF7" s="37"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="38"/>
-      <c r="AK7" s="38"/>
-      <c r="AL7" s="39"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="61"/>
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="62"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
       <c r="AO7" s="15"/>
     </row>
     <row r="8" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A8" s="31"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
       <c r="H8" s="7"/>
       <c r="I8" s="6" t="s">
         <v>28</v>
@@ -1522,25 +1603,25 @@
       <c r="AC8" s="6"/>
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="26"/>
-      <c r="AJ8" s="26"/>
-      <c r="AK8" s="26"/>
-      <c r="AL8" s="27"/>
+      <c r="AF8" s="55"/>
+      <c r="AG8" s="56"/>
+      <c r="AH8" s="56"/>
+      <c r="AI8" s="56"/>
+      <c r="AJ8" s="56"/>
+      <c r="AK8" s="56"/>
+      <c r="AL8" s="57"/>
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
       <c r="AO8" s="5"/>
     </row>
     <row r="9" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
       <c r="H9" s="7"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
@@ -1567,25 +1648,25 @@
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
       <c r="AE9" s="6"/>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="26"/>
-      <c r="AL9" s="27"/>
+      <c r="AF9" s="55"/>
+      <c r="AG9" s="56"/>
+      <c r="AH9" s="56"/>
+      <c r="AI9" s="56"/>
+      <c r="AJ9" s="56"/>
+      <c r="AK9" s="56"/>
+      <c r="AL9" s="57"/>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
       <c r="AO9" s="5"/>
     </row>
     <row r="10" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A10" s="31"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="7"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -1612,25 +1693,25 @@
       <c r="AC10" s="6"/>
       <c r="AD10" s="6"/>
       <c r="AE10" s="6"/>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="26"/>
-      <c r="AH10" s="26"/>
-      <c r="AI10" s="26"/>
-      <c r="AJ10" s="26"/>
-      <c r="AK10" s="26"/>
-      <c r="AL10" s="27"/>
+      <c r="AF10" s="55"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="56"/>
+      <c r="AJ10" s="56"/>
+      <c r="AK10" s="56"/>
+      <c r="AL10" s="57"/>
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
       <c r="AO10" s="5"/>
     </row>
     <row r="11" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A11" s="31"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
       <c r="H11" s="7"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -1657,25 +1738,25 @@
       <c r="AC11" s="6"/>
       <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="26"/>
-      <c r="AJ11" s="26"/>
-      <c r="AK11" s="26"/>
-      <c r="AL11" s="27"/>
+      <c r="AF11" s="55"/>
+      <c r="AG11" s="56"/>
+      <c r="AH11" s="56"/>
+      <c r="AI11" s="56"/>
+      <c r="AJ11" s="56"/>
+      <c r="AK11" s="56"/>
+      <c r="AL11" s="57"/>
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
       <c r="AO11" s="5"/>
     </row>
     <row r="12" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
       <c r="H12" s="7"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
@@ -1702,25 +1783,25 @@
       <c r="AC12" s="6"/>
       <c r="AD12" s="6"/>
       <c r="AE12" s="5"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
-      <c r="AH12" s="26"/>
-      <c r="AI12" s="26"/>
-      <c r="AJ12" s="26"/>
-      <c r="AK12" s="26"/>
-      <c r="AL12" s="27"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
+      <c r="AJ12" s="56"/>
+      <c r="AK12" s="56"/>
+      <c r="AL12" s="57"/>
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
       <c r="AO12" s="5"/>
     </row>
     <row r="13" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="7"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
@@ -1747,25 +1828,25 @@
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
       <c r="AE13" s="6"/>
-      <c r="AF13" s="25"/>
-      <c r="AG13" s="26"/>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="26"/>
-      <c r="AJ13" s="26"/>
-      <c r="AK13" s="26"/>
-      <c r="AL13" s="27"/>
+      <c r="AF13" s="55"/>
+      <c r="AG13" s="56"/>
+      <c r="AH13" s="56"/>
+      <c r="AI13" s="56"/>
+      <c r="AJ13" s="56"/>
+      <c r="AK13" s="56"/>
+      <c r="AL13" s="57"/>
       <c r="AM13" s="6"/>
       <c r="AN13" s="6"/>
       <c r="AO13" s="5"/>
     </row>
     <row r="14" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
       <c r="H14" s="7"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -1792,25 +1873,25 @@
       <c r="AC14" s="6"/>
       <c r="AD14" s="6"/>
       <c r="AE14" s="6"/>
-      <c r="AF14" s="25"/>
-      <c r="AG14" s="26"/>
-      <c r="AH14" s="26"/>
-      <c r="AI14" s="26"/>
-      <c r="AJ14" s="26"/>
-      <c r="AK14" s="26"/>
-      <c r="AL14" s="27"/>
+      <c r="AF14" s="55"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="57"/>
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
       <c r="AO14" s="5"/>
     </row>
     <row r="15" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
       <c r="H15" s="7"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -1837,25 +1918,25 @@
       <c r="AC15" s="6"/>
       <c r="AD15" s="6"/>
       <c r="AE15" s="6"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="26"/>
-      <c r="AI15" s="26"/>
-      <c r="AJ15" s="26"/>
-      <c r="AK15" s="26"/>
-      <c r="AL15" s="27"/>
+      <c r="AF15" s="55"/>
+      <c r="AG15" s="56"/>
+      <c r="AH15" s="56"/>
+      <c r="AI15" s="56"/>
+      <c r="AJ15" s="56"/>
+      <c r="AK15" s="56"/>
+      <c r="AL15" s="57"/>
       <c r="AM15" s="6"/>
       <c r="AN15" s="6"/>
       <c r="AO15" s="5"/>
     </row>
     <row r="16" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
       <c r="H16" s="7"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
@@ -1882,25 +1963,25 @@
       <c r="AC16" s="6"/>
       <c r="AD16" s="6"/>
       <c r="AE16" s="6"/>
-      <c r="AF16" s="25"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="26"/>
-      <c r="AI16" s="26"/>
-      <c r="AJ16" s="26"/>
-      <c r="AK16" s="26"/>
-      <c r="AL16" s="27"/>
+      <c r="AF16" s="55"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
+      <c r="AJ16" s="56"/>
+      <c r="AK16" s="56"/>
+      <c r="AL16" s="57"/>
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
       <c r="AO16" s="5"/>
     </row>
     <row r="17" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
       <c r="H17" s="7"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -1927,25 +2008,25 @@
       <c r="AC17" s="6"/>
       <c r="AD17" s="6"/>
       <c r="AE17" s="6"/>
-      <c r="AF17" s="25"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="26"/>
-      <c r="AI17" s="26"/>
-      <c r="AJ17" s="26"/>
-      <c r="AK17" s="26"/>
-      <c r="AL17" s="27"/>
+      <c r="AF17" s="55"/>
+      <c r="AG17" s="56"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="56"/>
+      <c r="AJ17" s="56"/>
+      <c r="AK17" s="56"/>
+      <c r="AL17" s="57"/>
       <c r="AM17" s="6"/>
       <c r="AN17" s="6"/>
       <c r="AO17" s="5"/>
     </row>
     <row r="18" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
       <c r="H18" s="7"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -1972,13 +2053,13 @@
       <c r="AC18" s="6"/>
       <c r="AD18" s="6"/>
       <c r="AE18" s="6"/>
-      <c r="AF18" s="25"/>
-      <c r="AG18" s="26"/>
-      <c r="AH18" s="26"/>
-      <c r="AI18" s="26"/>
-      <c r="AJ18" s="26"/>
-      <c r="AK18" s="26"/>
-      <c r="AL18" s="27"/>
+      <c r="AF18" s="55"/>
+      <c r="AG18" s="56"/>
+      <c r="AH18" s="56"/>
+      <c r="AI18" s="56"/>
+      <c r="AJ18" s="56"/>
+      <c r="AK18" s="56"/>
+      <c r="AL18" s="57"/>
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
       <c r="AO18" s="5"/>
@@ -2930,7 +3011,9 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="13"/>
-      <c r="L40" s="14"/>
+      <c r="L40" s="14" t="s">
+        <v>58</v>
+      </c>
       <c r="M40" s="14"/>
       <c r="N40" s="14"/>
       <c r="O40" s="14"/>
@@ -2962,18 +3045,20 @@
       <c r="AO40" s="5"/>
     </row>
     <row r="41" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="A41" s="25"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
       <c r="H41" s="7"/>
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="13"/>
-      <c r="L41" s="14"/>
+      <c r="L41" s="14" t="s">
+        <v>59</v>
+      </c>
       <c r="M41" s="14"/>
       <c r="N41" s="14"/>
       <c r="O41" s="14"/>
@@ -2988,35 +3073,37 @@
       <c r="X41" s="14"/>
       <c r="Y41" s="14"/>
       <c r="Z41" s="14"/>
-      <c r="AA41" s="9"/>
-      <c r="AB41" s="9"/>
-      <c r="AC41" s="9"/>
-      <c r="AD41" s="9"/>
+      <c r="AA41" s="26"/>
+      <c r="AB41" s="26"/>
+      <c r="AC41" s="26"/>
+      <c r="AD41" s="26"/>
       <c r="AE41" s="6"/>
-      <c r="AF41" s="10"/>
-      <c r="AG41" s="9"/>
-      <c r="AH41" s="9"/>
-      <c r="AI41" s="9"/>
-      <c r="AJ41" s="9"/>
-      <c r="AK41" s="9"/>
-      <c r="AL41" s="8"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="26"/>
+      <c r="AH41" s="26"/>
+      <c r="AI41" s="26"/>
+      <c r="AJ41" s="26"/>
+      <c r="AK41" s="26"/>
+      <c r="AL41" s="27"/>
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
       <c r="AO41" s="5"/>
     </row>
     <row r="42" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
       <c r="H42" s="7"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="13"/>
-      <c r="L42" s="14"/>
+      <c r="L42" s="14" t="s">
+        <v>61</v>
+      </c>
       <c r="M42" s="14"/>
       <c r="N42" s="14"/>
       <c r="O42" s="14"/>
@@ -3031,35 +3118,37 @@
       <c r="X42" s="14"/>
       <c r="Y42" s="14"/>
       <c r="Z42" s="14"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="9"/>
+      <c r="AA42" s="26"/>
+      <c r="AB42" s="26"/>
+      <c r="AC42" s="26"/>
+      <c r="AD42" s="26"/>
       <c r="AE42" s="6"/>
-      <c r="AF42" s="10"/>
-      <c r="AG42" s="9"/>
-      <c r="AH42" s="9"/>
-      <c r="AI42" s="9"/>
-      <c r="AJ42" s="9"/>
-      <c r="AK42" s="9"/>
-      <c r="AL42" s="8"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="26"/>
+      <c r="AH42" s="26"/>
+      <c r="AI42" s="26"/>
+      <c r="AJ42" s="26"/>
+      <c r="AK42" s="26"/>
+      <c r="AL42" s="27"/>
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
       <c r="AO42" s="5"/>
     </row>
     <row r="43" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A43" s="10"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
       <c r="H43" s="7"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="13"/>
-      <c r="L43" s="14"/>
+      <c r="L43" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="M43" s="14"/>
       <c r="N43" s="14"/>
       <c r="O43" s="14"/>
@@ -3074,35 +3163,37 @@
       <c r="X43" s="14"/>
       <c r="Y43" s="14"/>
       <c r="Z43" s="14"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="9"/>
+      <c r="AA43" s="26"/>
+      <c r="AB43" s="26"/>
+      <c r="AC43" s="26"/>
+      <c r="AD43" s="26"/>
       <c r="AE43" s="6"/>
-      <c r="AF43" s="10"/>
-      <c r="AG43" s="9"/>
-      <c r="AH43" s="9"/>
-      <c r="AI43" s="9"/>
-      <c r="AJ43" s="9"/>
-      <c r="AK43" s="9"/>
-      <c r="AL43" s="8"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="26"/>
+      <c r="AH43" s="26"/>
+      <c r="AI43" s="26"/>
+      <c r="AJ43" s="26"/>
+      <c r="AK43" s="26"/>
+      <c r="AL43" s="27"/>
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
       <c r="AO43" s="5"/>
     </row>
     <row r="44" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
       <c r="H44" s="7"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="13"/>
-      <c r="L44" s="14"/>
+      <c r="L44" s="14" t="s">
+        <v>66</v>
+      </c>
       <c r="M44" s="14"/>
       <c r="N44" s="14"/>
       <c r="O44" s="14"/>
@@ -3117,18 +3208,18 @@
       <c r="X44" s="14"/>
       <c r="Y44" s="14"/>
       <c r="Z44" s="14"/>
-      <c r="AA44" s="9"/>
-      <c r="AB44" s="9"/>
-      <c r="AC44" s="9"/>
-      <c r="AD44" s="9"/>
+      <c r="AA44" s="26"/>
+      <c r="AB44" s="26"/>
+      <c r="AC44" s="26"/>
+      <c r="AD44" s="26"/>
       <c r="AE44" s="6"/>
-      <c r="AF44" s="10"/>
-      <c r="AG44" s="9"/>
-      <c r="AH44" s="9"/>
-      <c r="AI44" s="9"/>
-      <c r="AJ44" s="9"/>
-      <c r="AK44" s="9"/>
-      <c r="AL44" s="8"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="26"/>
+      <c r="AH44" s="26"/>
+      <c r="AI44" s="26"/>
+      <c r="AJ44" s="26"/>
+      <c r="AK44" s="26"/>
+      <c r="AL44" s="27"/>
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
       <c r="AO44" s="5"/>
@@ -3187,26 +3278,28 @@
       <c r="H46" s="7"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="13"/>
-      <c r="R46" s="13"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="13"/>
-      <c r="U46" s="13"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="13"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46" s="13"/>
-      <c r="AB46" s="13"/>
-      <c r="AC46" s="13"/>
-      <c r="AD46" s="13"/>
+      <c r="K46" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+      <c r="Q46" s="14"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="14"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+      <c r="X46" s="14"/>
+      <c r="Y46" s="14"/>
+      <c r="Z46" s="14"/>
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
+      <c r="AD46" s="9"/>
       <c r="AE46" s="6"/>
       <c r="AF46" s="10"/>
       <c r="AG46" s="9"/>
@@ -3231,25 +3324,27 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="13"/>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="13"/>
-      <c r="AB47" s="13"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="13"/>
+      <c r="L47" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+      <c r="Z47" s="14"/>
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+      <c r="AD47" s="9"/>
       <c r="AE47" s="6"/>
       <c r="AF47" s="10"/>
       <c r="AG47" s="9"/>
@@ -3274,25 +3369,27 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="13"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="13"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48" s="13"/>
-      <c r="AB48" s="13"/>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="13"/>
+      <c r="L48" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="14"/>
+      <c r="P48" s="14"/>
+      <c r="Q48" s="14"/>
+      <c r="R48" s="14"/>
+      <c r="S48" s="14"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="14"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="14"/>
+      <c r="X48" s="14"/>
+      <c r="Y48" s="14"/>
+      <c r="Z48" s="14"/>
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+      <c r="AD48" s="9"/>
       <c r="AE48" s="6"/>
       <c r="AF48" s="10"/>
       <c r="AG48" s="9"/>
@@ -3317,25 +3414,27 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
       <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="13"/>
-      <c r="AB49" s="13"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
+      <c r="L49" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+      <c r="P49" s="14"/>
+      <c r="Q49" s="14"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="14"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="14"/>
+      <c r="X49" s="14"/>
+      <c r="Y49" s="14"/>
+      <c r="Z49" s="14"/>
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9"/>
+      <c r="AD49" s="9"/>
       <c r="AE49" s="6"/>
       <c r="AF49" s="10"/>
       <c r="AG49" s="9"/>
@@ -3360,7 +3459,9 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
       <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
+      <c r="L50" s="13" t="s">
+        <v>65</v>
+      </c>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
       <c r="O50" s="13"/>
@@ -3489,25 +3590,25 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="13"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="6"/>
-      <c r="AB53" s="6"/>
-      <c r="AC53" s="6"/>
-      <c r="AD53" s="6"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="13"/>
+      <c r="U53" s="13"/>
+      <c r="V53" s="13"/>
+      <c r="W53" s="13"/>
+      <c r="X53" s="13"/>
+      <c r="Y53" s="13"/>
+      <c r="Z53" s="13"/>
+      <c r="AA53" s="13"/>
+      <c r="AB53" s="13"/>
+      <c r="AC53" s="13"/>
+      <c r="AD53" s="13"/>
       <c r="AE53" s="6"/>
       <c r="AF53" s="10"/>
       <c r="AG53" s="9"/>
@@ -3532,25 +3633,25 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
       <c r="K54" s="13"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="6"/>
-      <c r="AB54" s="6"/>
-      <c r="AC54" s="6"/>
-      <c r="AD54" s="6"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="13"/>
+      <c r="U54" s="13"/>
+      <c r="V54" s="13"/>
+      <c r="W54" s="13"/>
+      <c r="X54" s="13"/>
+      <c r="Y54" s="13"/>
+      <c r="Z54" s="13"/>
+      <c r="AA54" s="13"/>
+      <c r="AB54" s="13"/>
+      <c r="AC54" s="13"/>
+      <c r="AD54" s="13"/>
       <c r="AE54" s="6"/>
       <c r="AF54" s="10"/>
       <c r="AG54" s="9"/>
@@ -3575,25 +3676,25 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
       <c r="K55" s="13"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="6"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="6"/>
-      <c r="AB55" s="6"/>
-      <c r="AC55" s="6"/>
-      <c r="AD55" s="6"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="13"/>
+      <c r="U55" s="13"/>
+      <c r="V55" s="13"/>
+      <c r="W55" s="13"/>
+      <c r="X55" s="13"/>
+      <c r="Y55" s="13"/>
+      <c r="Z55" s="13"/>
+      <c r="AA55" s="13"/>
+      <c r="AB55" s="13"/>
+      <c r="AC55" s="13"/>
+      <c r="AD55" s="13"/>
       <c r="AE55" s="6"/>
       <c r="AF55" s="10"/>
       <c r="AG55" s="9"/>
@@ -3618,25 +3719,25 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
       <c r="K56" s="13"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="6"/>
-      <c r="X56" s="6"/>
-      <c r="Y56" s="6"/>
-      <c r="Z56" s="6"/>
-      <c r="AA56" s="6"/>
-      <c r="AB56" s="6"/>
-      <c r="AC56" s="6"/>
-      <c r="AD56" s="6"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="13"/>
+      <c r="U56" s="13"/>
+      <c r="V56" s="13"/>
+      <c r="W56" s="13"/>
+      <c r="X56" s="13"/>
+      <c r="Y56" s="13"/>
+      <c r="Z56" s="13"/>
+      <c r="AA56" s="13"/>
+      <c r="AB56" s="13"/>
+      <c r="AC56" s="13"/>
+      <c r="AD56" s="13"/>
       <c r="AE56" s="6"/>
       <c r="AF56" s="10"/>
       <c r="AG56" s="9"/>
@@ -3650,13 +3751,13 @@
       <c r="AO56" s="5"/>
     </row>
     <row r="57" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A57" s="25"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
       <c r="H57" s="7"/>
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
@@ -3681,25 +3782,25 @@
       <c r="AC57" s="6"/>
       <c r="AD57" s="6"/>
       <c r="AE57" s="6"/>
-      <c r="AF57" s="25"/>
-      <c r="AG57" s="26"/>
-      <c r="AH57" s="26"/>
-      <c r="AI57" s="26"/>
-      <c r="AJ57" s="26"/>
-      <c r="AK57" s="26"/>
-      <c r="AL57" s="27"/>
+      <c r="AF57" s="10"/>
+      <c r="AG57" s="9"/>
+      <c r="AH57" s="9"/>
+      <c r="AI57" s="9"/>
+      <c r="AJ57" s="9"/>
+      <c r="AK57" s="9"/>
+      <c r="AL57" s="8"/>
       <c r="AM57" s="6"/>
       <c r="AN57" s="6"/>
       <c r="AO57" s="5"/>
     </row>
     <row r="58" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A58" s="25"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
       <c r="H58" s="7"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
@@ -3724,25 +3825,25 @@
       <c r="AC58" s="6"/>
       <c r="AD58" s="6"/>
       <c r="AE58" s="6"/>
-      <c r="AF58" s="25"/>
-      <c r="AG58" s="26"/>
-      <c r="AH58" s="26"/>
-      <c r="AI58" s="26"/>
-      <c r="AJ58" s="26"/>
-      <c r="AK58" s="26"/>
-      <c r="AL58" s="27"/>
+      <c r="AF58" s="10"/>
+      <c r="AG58" s="9"/>
+      <c r="AH58" s="9"/>
+      <c r="AI58" s="9"/>
+      <c r="AJ58" s="9"/>
+      <c r="AK58" s="9"/>
+      <c r="AL58" s="8"/>
       <c r="AM58" s="6"/>
       <c r="AN58" s="6"/>
       <c r="AO58" s="5"/>
     </row>
     <row r="59" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A59" s="25"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
       <c r="H59" s="7"/>
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
@@ -3767,30 +3868,30 @@
       <c r="AC59" s="6"/>
       <c r="AD59" s="6"/>
       <c r="AE59" s="6"/>
-      <c r="AF59" s="25"/>
-      <c r="AG59" s="26"/>
-      <c r="AH59" s="26"/>
-      <c r="AI59" s="26"/>
-      <c r="AJ59" s="26"/>
-      <c r="AK59" s="26"/>
-      <c r="AL59" s="27"/>
+      <c r="AF59" s="10"/>
+      <c r="AG59" s="9"/>
+      <c r="AH59" s="9"/>
+      <c r="AI59" s="9"/>
+      <c r="AJ59" s="9"/>
+      <c r="AK59" s="9"/>
+      <c r="AL59" s="8"/>
       <c r="AM59" s="6"/>
       <c r="AN59" s="6"/>
       <c r="AO59" s="5"/>
     </row>
     <row r="60" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A60" s="25"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
       <c r="H60" s="7"/>
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" s="13"/>
-      <c r="L60" s="12"/>
+      <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
       <c r="O60" s="6"/>
@@ -3810,30 +3911,30 @@
       <c r="AC60" s="6"/>
       <c r="AD60" s="6"/>
       <c r="AE60" s="6"/>
-      <c r="AF60" s="25"/>
-      <c r="AG60" s="26"/>
-      <c r="AH60" s="26"/>
-      <c r="AI60" s="26"/>
-      <c r="AJ60" s="26"/>
-      <c r="AK60" s="26"/>
-      <c r="AL60" s="27"/>
+      <c r="AF60" s="10"/>
+      <c r="AG60" s="9"/>
+      <c r="AH60" s="9"/>
+      <c r="AI60" s="9"/>
+      <c r="AJ60" s="9"/>
+      <c r="AK60" s="9"/>
+      <c r="AL60" s="8"/>
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
       <c r="AO60" s="5"/>
     </row>
     <row r="61" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A61" s="31"/>
-      <c r="B61" s="32"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
+      <c r="A61" s="55"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
       <c r="H61" s="7"/>
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="13"/>
-      <c r="L61" s="12"/>
+      <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
@@ -3853,30 +3954,30 @@
       <c r="AC61" s="6"/>
       <c r="AD61" s="6"/>
       <c r="AE61" s="6"/>
-      <c r="AF61" s="25"/>
-      <c r="AG61" s="26"/>
-      <c r="AH61" s="26"/>
-      <c r="AI61" s="26"/>
-      <c r="AJ61" s="26"/>
-      <c r="AK61" s="26"/>
-      <c r="AL61" s="27"/>
+      <c r="AF61" s="55"/>
+      <c r="AG61" s="56"/>
+      <c r="AH61" s="56"/>
+      <c r="AI61" s="56"/>
+      <c r="AJ61" s="56"/>
+      <c r="AK61" s="56"/>
+      <c r="AL61" s="57"/>
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
       <c r="AO61" s="5"/>
     </row>
     <row r="62" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A62" s="31"/>
-      <c r="B62" s="32"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
+      <c r="A62" s="55"/>
+      <c r="B62" s="56"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="56"/>
+      <c r="G62" s="56"/>
       <c r="H62" s="7"/>
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="13"/>
-      <c r="L62" s="12"/>
+      <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
       <c r="O62" s="6"/>
@@ -3896,30 +3997,30 @@
       <c r="AC62" s="6"/>
       <c r="AD62" s="6"/>
       <c r="AE62" s="6"/>
-      <c r="AF62" s="25"/>
-      <c r="AG62" s="26"/>
-      <c r="AH62" s="26"/>
-      <c r="AI62" s="26"/>
-      <c r="AJ62" s="26"/>
-      <c r="AK62" s="26"/>
-      <c r="AL62" s="27"/>
+      <c r="AF62" s="55"/>
+      <c r="AG62" s="56"/>
+      <c r="AH62" s="56"/>
+      <c r="AI62" s="56"/>
+      <c r="AJ62" s="56"/>
+      <c r="AK62" s="56"/>
+      <c r="AL62" s="57"/>
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
       <c r="AO62" s="5"/>
     </row>
     <row r="63" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A63" s="25"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
+      <c r="A63" s="55"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
       <c r="H63" s="7"/>
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="12"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
       <c r="O63" s="6"/>
@@ -3939,29 +4040,29 @@
       <c r="AC63" s="6"/>
       <c r="AD63" s="6"/>
       <c r="AE63" s="6"/>
-      <c r="AF63" s="25"/>
-      <c r="AG63" s="26"/>
-      <c r="AH63" s="26"/>
-      <c r="AI63" s="26"/>
-      <c r="AJ63" s="26"/>
-      <c r="AK63" s="26"/>
-      <c r="AL63" s="27"/>
+      <c r="AF63" s="55"/>
+      <c r="AG63" s="56"/>
+      <c r="AH63" s="56"/>
+      <c r="AI63" s="56"/>
+      <c r="AJ63" s="56"/>
+      <c r="AK63" s="56"/>
+      <c r="AL63" s="57"/>
       <c r="AM63" s="6"/>
       <c r="AN63" s="6"/>
       <c r="AO63" s="5"/>
     </row>
     <row r="64" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A64" s="25"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
+      <c r="A64" s="55"/>
+      <c r="B64" s="56"/>
+      <c r="C64" s="56"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
       <c r="H64" s="7"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
+      <c r="K64" s="13"/>
       <c r="L64" s="12"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
@@ -3982,29 +4083,29 @@
       <c r="AC64" s="6"/>
       <c r="AD64" s="6"/>
       <c r="AE64" s="6"/>
-      <c r="AF64" s="25"/>
-      <c r="AG64" s="26"/>
-      <c r="AH64" s="26"/>
-      <c r="AI64" s="26"/>
-      <c r="AJ64" s="26"/>
-      <c r="AK64" s="26"/>
-      <c r="AL64" s="27"/>
+      <c r="AF64" s="55"/>
+      <c r="AG64" s="56"/>
+      <c r="AH64" s="56"/>
+      <c r="AI64" s="56"/>
+      <c r="AJ64" s="56"/>
+      <c r="AK64" s="56"/>
+      <c r="AL64" s="57"/>
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
       <c r="AO64" s="5"/>
     </row>
     <row r="65" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A65" s="10"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
+      <c r="A65" s="53"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
       <c r="H65" s="7"/>
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
+      <c r="K65" s="13"/>
       <c r="L65" s="12"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
@@ -4025,30 +4126,30 @@
       <c r="AC65" s="6"/>
       <c r="AD65" s="6"/>
       <c r="AE65" s="6"/>
-      <c r="AF65" s="10"/>
-      <c r="AG65" s="9"/>
-      <c r="AH65" s="9"/>
-      <c r="AI65" s="9"/>
-      <c r="AJ65" s="9"/>
-      <c r="AK65" s="9"/>
-      <c r="AL65" s="8"/>
+      <c r="AF65" s="55"/>
+      <c r="AG65" s="56"/>
+      <c r="AH65" s="56"/>
+      <c r="AI65" s="56"/>
+      <c r="AJ65" s="56"/>
+      <c r="AK65" s="56"/>
+      <c r="AL65" s="57"/>
       <c r="AM65" s="6"/>
       <c r="AN65" s="6"/>
       <c r="AO65" s="5"/>
     </row>
     <row r="66" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A66" s="10"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
+      <c r="A66" s="53"/>
+      <c r="B66" s="54"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="54"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="54"/>
       <c r="H66" s="7"/>
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="12"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
       <c r="O66" s="6"/>
@@ -4068,30 +4169,30 @@
       <c r="AC66" s="6"/>
       <c r="AD66" s="6"/>
       <c r="AE66" s="6"/>
-      <c r="AF66" s="10"/>
-      <c r="AG66" s="9"/>
-      <c r="AH66" s="9"/>
-      <c r="AI66" s="9"/>
-      <c r="AJ66" s="9"/>
-      <c r="AK66" s="9"/>
-      <c r="AL66" s="8"/>
+      <c r="AF66" s="55"/>
+      <c r="AG66" s="56"/>
+      <c r="AH66" s="56"/>
+      <c r="AI66" s="56"/>
+      <c r="AJ66" s="56"/>
+      <c r="AK66" s="56"/>
+      <c r="AL66" s="57"/>
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
       <c r="AO66" s="5"/>
     </row>
     <row r="67" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A67" s="10"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
+      <c r="A67" s="55"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
       <c r="H67" s="7"/>
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="11"/>
-      <c r="L67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="12"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
       <c r="O67" s="6"/>
@@ -4111,30 +4212,30 @@
       <c r="AC67" s="6"/>
       <c r="AD67" s="6"/>
       <c r="AE67" s="6"/>
-      <c r="AF67" s="10"/>
-      <c r="AG67" s="9"/>
-      <c r="AH67" s="9"/>
-      <c r="AI67" s="9"/>
-      <c r="AJ67" s="9"/>
-      <c r="AK67" s="9"/>
-      <c r="AL67" s="8"/>
+      <c r="AF67" s="55"/>
+      <c r="AG67" s="56"/>
+      <c r="AH67" s="56"/>
+      <c r="AI67" s="56"/>
+      <c r="AJ67" s="56"/>
+      <c r="AK67" s="56"/>
+      <c r="AL67" s="57"/>
       <c r="AM67" s="6"/>
       <c r="AN67" s="6"/>
       <c r="AO67" s="5"/>
     </row>
     <row r="68" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A68" s="25"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
-      <c r="D68" s="26"/>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
+      <c r="A68" s="55"/>
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
       <c r="H68" s="7"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
+      <c r="L68" s="12"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
@@ -4154,30 +4255,30 @@
       <c r="AC68" s="6"/>
       <c r="AD68" s="6"/>
       <c r="AE68" s="6"/>
-      <c r="AF68" s="25"/>
-      <c r="AG68" s="26"/>
-      <c r="AH68" s="26"/>
-      <c r="AI68" s="26"/>
-      <c r="AJ68" s="26"/>
-      <c r="AK68" s="26"/>
-      <c r="AL68" s="27"/>
+      <c r="AF68" s="55"/>
+      <c r="AG68" s="56"/>
+      <c r="AH68" s="56"/>
+      <c r="AI68" s="56"/>
+      <c r="AJ68" s="56"/>
+      <c r="AK68" s="56"/>
+      <c r="AL68" s="57"/>
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
       <c r="AO68" s="5"/>
     </row>
     <row r="69" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A69" s="25"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
       <c r="H69" s="7"/>
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
+      <c r="L69" s="12"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
       <c r="O69" s="6"/>
@@ -4197,183 +4298,348 @@
       <c r="AC69" s="6"/>
       <c r="AD69" s="6"/>
       <c r="AE69" s="6"/>
-      <c r="AF69" s="25"/>
-      <c r="AG69" s="26"/>
-      <c r="AH69" s="26"/>
-      <c r="AI69" s="26"/>
-      <c r="AJ69" s="26"/>
-      <c r="AK69" s="26"/>
-      <c r="AL69" s="27"/>
+      <c r="AF69" s="10"/>
+      <c r="AG69" s="9"/>
+      <c r="AH69" s="9"/>
+      <c r="AI69" s="9"/>
+      <c r="AJ69" s="9"/>
+      <c r="AK69" s="9"/>
+      <c r="AL69" s="8"/>
       <c r="AM69" s="6"/>
       <c r="AN69" s="6"/>
       <c r="AO69" s="5"/>
     </row>
     <row r="70" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A70" s="25"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
       <c r="H70" s="7"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
-      <c r="AB70" s="3"/>
-      <c r="AC70" s="3"/>
-      <c r="AD70" s="3"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+      <c r="T70" s="6"/>
+      <c r="U70" s="6"/>
+      <c r="V70" s="6"/>
+      <c r="W70" s="6"/>
+      <c r="X70" s="6"/>
+      <c r="Y70" s="6"/>
+      <c r="Z70" s="6"/>
+      <c r="AA70" s="6"/>
+      <c r="AB70" s="6"/>
+      <c r="AC70" s="6"/>
+      <c r="AD70" s="6"/>
       <c r="AE70" s="6"/>
-      <c r="AF70" s="25"/>
-      <c r="AG70" s="26"/>
-      <c r="AH70" s="26"/>
-      <c r="AI70" s="26"/>
-      <c r="AJ70" s="26"/>
-      <c r="AK70" s="26"/>
-      <c r="AL70" s="27"/>
+      <c r="AF70" s="10"/>
+      <c r="AG70" s="9"/>
+      <c r="AH70" s="9"/>
+      <c r="AI70" s="9"/>
+      <c r="AJ70" s="9"/>
+      <c r="AK70" s="9"/>
+      <c r="AL70" s="8"/>
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
       <c r="AO70" s="5"/>
     </row>
     <row r="71" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A71" s="25"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
       <c r="H71" s="7"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="6"/>
+      <c r="T71" s="6"/>
+      <c r="U71" s="6"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6"/>
+      <c r="X71" s="6"/>
+      <c r="Y71" s="6"/>
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6"/>
+      <c r="AB71" s="6"/>
+      <c r="AC71" s="6"/>
+      <c r="AD71" s="6"/>
       <c r="AE71" s="6"/>
-      <c r="AF71" s="25"/>
-      <c r="AG71" s="26"/>
-      <c r="AH71" s="26"/>
-      <c r="AI71" s="26"/>
-      <c r="AJ71" s="26"/>
-      <c r="AK71" s="26"/>
-      <c r="AL71" s="27"/>
+      <c r="AF71" s="10"/>
+      <c r="AG71" s="9"/>
+      <c r="AH71" s="9"/>
+      <c r="AI71" s="9"/>
+      <c r="AJ71" s="9"/>
+      <c r="AK71" s="9"/>
+      <c r="AL71" s="8"/>
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
       <c r="AO71" s="5"/>
     </row>
     <row r="72" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A72" s="25"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="26"/>
+      <c r="A72" s="55"/>
+      <c r="B72" s="56"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="56"/>
+      <c r="F72" s="56"/>
+      <c r="G72" s="56"/>
       <c r="H72" s="7"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
+      <c r="V72" s="6"/>
+      <c r="W72" s="6"/>
+      <c r="X72" s="6"/>
+      <c r="Y72" s="6"/>
+      <c r="Z72" s="6"/>
+      <c r="AA72" s="6"/>
+      <c r="AB72" s="6"/>
+      <c r="AC72" s="6"/>
+      <c r="AD72" s="6"/>
       <c r="AE72" s="6"/>
-      <c r="AF72" s="25"/>
-      <c r="AG72" s="26"/>
-      <c r="AH72" s="26"/>
-      <c r="AI72" s="26"/>
-      <c r="AJ72" s="26"/>
-      <c r="AK72" s="26"/>
-      <c r="AL72" s="27"/>
+      <c r="AF72" s="55"/>
+      <c r="AG72" s="56"/>
+      <c r="AH72" s="56"/>
+      <c r="AI72" s="56"/>
+      <c r="AJ72" s="56"/>
+      <c r="AK72" s="56"/>
+      <c r="AL72" s="57"/>
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
       <c r="AO72" s="5"/>
     </row>
     <row r="73" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A73" s="25"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
+      <c r="A73" s="55"/>
+      <c r="B73" s="56"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="56"/>
+      <c r="E73" s="56"/>
+      <c r="F73" s="56"/>
+      <c r="G73" s="56"/>
       <c r="H73" s="7"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+      <c r="R73" s="6"/>
+      <c r="S73" s="6"/>
+      <c r="T73" s="6"/>
+      <c r="U73" s="6"/>
+      <c r="V73" s="6"/>
+      <c r="W73" s="6"/>
+      <c r="X73" s="6"/>
+      <c r="Y73" s="6"/>
+      <c r="Z73" s="6"/>
+      <c r="AA73" s="6"/>
+      <c r="AB73" s="6"/>
+      <c r="AC73" s="6"/>
+      <c r="AD73" s="6"/>
       <c r="AE73" s="6"/>
-      <c r="AF73" s="25"/>
-      <c r="AG73" s="26"/>
-      <c r="AH73" s="26"/>
-      <c r="AI73" s="26"/>
-      <c r="AJ73" s="26"/>
-      <c r="AK73" s="26"/>
-      <c r="AL73" s="27"/>
+      <c r="AF73" s="55"/>
+      <c r="AG73" s="56"/>
+      <c r="AH73" s="56"/>
+      <c r="AI73" s="56"/>
+      <c r="AJ73" s="56"/>
+      <c r="AK73" s="56"/>
+      <c r="AL73" s="57"/>
       <c r="AM73" s="6"/>
       <c r="AN73" s="6"/>
       <c r="AO73" s="5"/>
     </row>
     <row r="74" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A74" s="28"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="4"/>
-      <c r="AE74" s="3"/>
-      <c r="AF74" s="28"/>
-      <c r="AG74" s="29"/>
-      <c r="AH74" s="29"/>
-      <c r="AI74" s="29"/>
-      <c r="AJ74" s="29"/>
-      <c r="AK74" s="29"/>
-      <c r="AL74" s="30"/>
-      <c r="AM74" s="3"/>
-      <c r="AN74" s="3"/>
-      <c r="AO74" s="2"/>
+      <c r="A74" s="55"/>
+      <c r="B74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="3"/>
+      <c r="AA74" s="3"/>
+      <c r="AB74" s="3"/>
+      <c r="AC74" s="3"/>
+      <c r="AD74" s="3"/>
+      <c r="AE74" s="6"/>
+      <c r="AF74" s="55"/>
+      <c r="AG74" s="56"/>
+      <c r="AH74" s="56"/>
+      <c r="AI74" s="56"/>
+      <c r="AJ74" s="56"/>
+      <c r="AK74" s="56"/>
+      <c r="AL74" s="57"/>
+      <c r="AM74" s="6"/>
+      <c r="AN74" s="6"/>
+      <c r="AO74" s="5"/>
+    </row>
+    <row r="75" spans="1:41" ht="19.95" customHeight="1">
+      <c r="A75" s="55"/>
+      <c r="B75" s="56"/>
+      <c r="C75" s="56"/>
+      <c r="D75" s="56"/>
+      <c r="E75" s="56"/>
+      <c r="F75" s="56"/>
+      <c r="G75" s="56"/>
+      <c r="H75" s="7"/>
+      <c r="AE75" s="6"/>
+      <c r="AF75" s="55"/>
+      <c r="AG75" s="56"/>
+      <c r="AH75" s="56"/>
+      <c r="AI75" s="56"/>
+      <c r="AJ75" s="56"/>
+      <c r="AK75" s="56"/>
+      <c r="AL75" s="57"/>
+      <c r="AM75" s="6"/>
+      <c r="AN75" s="6"/>
+      <c r="AO75" s="5"/>
+    </row>
+    <row r="76" spans="1:41" ht="19.95" customHeight="1">
+      <c r="A76" s="55"/>
+      <c r="B76" s="56"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="7"/>
+      <c r="AE76" s="6"/>
+      <c r="AF76" s="55"/>
+      <c r="AG76" s="56"/>
+      <c r="AH76" s="56"/>
+      <c r="AI76" s="56"/>
+      <c r="AJ76" s="56"/>
+      <c r="AK76" s="56"/>
+      <c r="AL76" s="57"/>
+      <c r="AM76" s="6"/>
+      <c r="AN76" s="6"/>
+      <c r="AO76" s="5"/>
+    </row>
+    <row r="77" spans="1:41" ht="19.95" customHeight="1">
+      <c r="A77" s="55"/>
+      <c r="B77" s="56"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="7"/>
+      <c r="AE77" s="6"/>
+      <c r="AF77" s="55"/>
+      <c r="AG77" s="56"/>
+      <c r="AH77" s="56"/>
+      <c r="AI77" s="56"/>
+      <c r="AJ77" s="56"/>
+      <c r="AK77" s="56"/>
+      <c r="AL77" s="57"/>
+      <c r="AM77" s="6"/>
+      <c r="AN77" s="6"/>
+      <c r="AO77" s="5"/>
+    </row>
+    <row r="78" spans="1:41" ht="19.95" customHeight="1">
+      <c r="A78" s="63"/>
+      <c r="B78" s="64"/>
+      <c r="C78" s="64"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="4"/>
+      <c r="AE78" s="3"/>
+      <c r="AF78" s="63"/>
+      <c r="AG78" s="64"/>
+      <c r="AH78" s="64"/>
+      <c r="AI78" s="64"/>
+      <c r="AJ78" s="64"/>
+      <c r="AK78" s="64"/>
+      <c r="AL78" s="65"/>
+      <c r="AM78" s="3"/>
+      <c r="AN78" s="3"/>
+      <c r="AO78" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:AE6"/>
-    <mergeCell ref="AI1:AK2"/>
-    <mergeCell ref="T4:AA4"/>
-    <mergeCell ref="AL1:AO2"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="T3:AA3"/>
-    <mergeCell ref="AB3:AD4"/>
-    <mergeCell ref="AE3:AH4"/>
-    <mergeCell ref="AI3:AK4"/>
-    <mergeCell ref="AL3:AO4"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="A1:N4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AB1:AD2"/>
-    <mergeCell ref="AE1:AH2"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="AF9:AL9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="AF10:AL10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="AF11:AL11"/>
-    <mergeCell ref="AF6:AL6"/>
-    <mergeCell ref="AM6:AO6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="AF7:AL7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="AF8:AL8"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="AF59:AL59"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="AF73:AL73"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="AF74:AL74"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="AF75:AL75"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="AF76:AL76"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="AF77:AL77"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="AF78:AL78"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="AF68:AL68"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="AF72:AL72"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="AF64:AL64"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="AF65:AL65"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="AF66:AL66"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="AF61:AL61"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="AF62:AL62"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="AF67:AL67"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="AF63:AL63"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="AF12:AL12"/>
     <mergeCell ref="A13:G13"/>
@@ -4388,34 +4654,41 @@
     <mergeCell ref="AF17:AL17"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="AF18:AL18"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="AF57:AL57"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="AF58:AL58"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="AF63:AL63"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="AF64:AL64"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="AF68:AL68"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="AF60:AL60"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="AF61:AL61"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="AF62:AL62"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="AF72:AL72"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="AF73:AL73"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="AF74:AL74"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="AF69:AL69"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="AF70:AL70"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="AF71:AL71"/>
+    <mergeCell ref="AF6:AL6"/>
+    <mergeCell ref="AM6:AO6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AF7:AL7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="AF8:AL8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="AF9:AL9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="AF10:AL10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="AF11:AL11"/>
+    <mergeCell ref="A1:N4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AD2"/>
+    <mergeCell ref="AE1:AH2"/>
+    <mergeCell ref="AI1:AK2"/>
+    <mergeCell ref="T4:AA4"/>
+    <mergeCell ref="AL1:AO2"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="T3:AA3"/>
+    <mergeCell ref="AB3:AD4"/>
+    <mergeCell ref="AE3:AH4"/>
+    <mergeCell ref="AI3:AK4"/>
+    <mergeCell ref="AL3:AO4"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:AE6"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4432,234 +4705,234 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="49" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="50" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="49" t="s">
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="53" t="s">
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="49" t="s">
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="54">
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="39">
         <v>45566</v>
       </c>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
     </row>
     <row r="2" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="49" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="50" t="s">
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="52"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="53"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="40"/>
+      <c r="AM2" s="40"/>
+      <c r="AN2" s="40"/>
+      <c r="AO2" s="40"/>
     </row>
     <row r="3" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="49" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="53" t="s">
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="49" t="s">
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="53" t="s">
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="AF3" s="53"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="49" t="s">
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
-      <c r="AL3" s="54">
+      <c r="AJ3" s="37"/>
+      <c r="AK3" s="37"/>
+      <c r="AL3" s="39">
         <v>45609</v>
       </c>
-      <c r="AM3" s="55"/>
-      <c r="AN3" s="55"/>
-      <c r="AO3" s="55"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="40"/>
     </row>
     <row r="4" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="49" t="s">
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="53" t="s">
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="53"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="53"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="53"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="53"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="53"/>
-      <c r="AH4" s="53"/>
-      <c r="AI4" s="49"/>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
-      <c r="AL4" s="55"/>
-      <c r="AM4" s="55"/>
-      <c r="AN4" s="55"/>
-      <c r="AO4" s="55"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="37"/>
+      <c r="AC4" s="37"/>
+      <c r="AD4" s="37"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="37"/>
+      <c r="AJ4" s="37"/>
+      <c r="AK4" s="37"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
     </row>
     <row r="5" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="56" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="57"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="34" t="s">
+      <c r="E5" s="30"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="59" t="s">
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
       <c r="O5" s="18"/>
       <c r="P5" s="18"/>
       <c r="Q5" s="18"/>
@@ -4689,51 +4962,51 @@
       <c r="AO5" s="18"/>
     </row>
     <row r="6" spans="1:41" ht="19.95" customHeight="1">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="70"/>
-      <c r="Y6" s="70"/>
-      <c r="Z6" s="70"/>
-      <c r="AA6" s="70"/>
-      <c r="AB6" s="70"/>
-      <c r="AC6" s="70"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="70"/>
-      <c r="AF6" s="70"/>
-      <c r="AG6" s="70"/>
-      <c r="AH6" s="70"/>
-      <c r="AI6" s="70"/>
-      <c r="AJ6" s="70"/>
-      <c r="AK6" s="70"/>
-      <c r="AL6" s="71"/>
-      <c r="AM6" s="34" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="67"/>
+      <c r="AL6" s="68"/>
+      <c r="AM6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="AN6" s="34"/>
-      <c r="AO6" s="34"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
     </row>
     <row r="7" spans="1:41" ht="19.95" customHeight="1">
       <c r="A7" s="19"/>
@@ -4808,337 +5081,337 @@
     </row>
     <row r="9" spans="1:41" ht="19.95" customHeight="1">
       <c r="A9" s="22"/>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="67"/>
-      <c r="P9" s="67"/>
-      <c r="Q9" s="67"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="67"/>
-      <c r="T9" s="67"/>
-      <c r="U9" s="67"/>
-      <c r="V9" s="67"/>
-      <c r="W9" s="67"/>
-      <c r="X9" s="68"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="73"/>
+      <c r="T9" s="73"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="74"/>
       <c r="AM9" s="22"/>
       <c r="AO9" s="23"/>
     </row>
     <row r="10" spans="1:41" ht="19.95" customHeight="1">
       <c r="A10" s="22"/>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="64"/>
-      <c r="O10" s="64"/>
-      <c r="P10" s="64"/>
-      <c r="Q10" s="64"/>
-      <c r="R10" s="64"/>
-      <c r="S10" s="64"/>
-      <c r="T10" s="64"/>
-      <c r="U10" s="64"/>
-      <c r="V10" s="64"/>
-      <c r="W10" s="64"/>
-      <c r="X10" s="65"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="70"/>
+      <c r="V10" s="70"/>
+      <c r="W10" s="70"/>
+      <c r="X10" s="71"/>
       <c r="AM10" s="22"/>
       <c r="AO10" s="23"/>
     </row>
     <row r="11" spans="1:41" ht="19.95" customHeight="1">
       <c r="A11" s="22"/>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="64"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="64"/>
-      <c r="Q11" s="64"/>
-      <c r="R11" s="64"/>
-      <c r="S11" s="64"/>
-      <c r="T11" s="64"/>
-      <c r="U11" s="64"/>
-      <c r="V11" s="64"/>
-      <c r="W11" s="64"/>
-      <c r="X11" s="65"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="71"/>
       <c r="AM11" s="22"/>
       <c r="AO11" s="23"/>
     </row>
     <row r="12" spans="1:41" ht="19.95" customHeight="1">
       <c r="A12" s="22"/>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="64"/>
-      <c r="P12" s="64"/>
-      <c r="Q12" s="64"/>
-      <c r="R12" s="64"/>
-      <c r="S12" s="64"/>
-      <c r="T12" s="64"/>
-      <c r="U12" s="64"/>
-      <c r="V12" s="64"/>
-      <c r="W12" s="64"/>
-      <c r="X12" s="65"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+      <c r="Q12" s="70"/>
+      <c r="R12" s="70"/>
+      <c r="S12" s="70"/>
+      <c r="T12" s="70"/>
+      <c r="U12" s="70"/>
+      <c r="V12" s="70"/>
+      <c r="W12" s="70"/>
+      <c r="X12" s="71"/>
       <c r="AM12" s="22"/>
       <c r="AO12" s="23"/>
     </row>
     <row r="13" spans="1:41" ht="19.95" customHeight="1">
       <c r="A13" s="22"/>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="64"/>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="64"/>
-      <c r="V13" s="64"/>
-      <c r="W13" s="64"/>
-      <c r="X13" s="65"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="70"/>
+      <c r="T13" s="70"/>
+      <c r="U13" s="70"/>
+      <c r="V13" s="70"/>
+      <c r="W13" s="70"/>
+      <c r="X13" s="71"/>
       <c r="AM13" s="22"/>
       <c r="AO13" s="23"/>
     </row>
     <row r="14" spans="1:41" ht="19.95" customHeight="1">
       <c r="A14" s="22"/>
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="64"/>
-      <c r="Q14" s="64"/>
-      <c r="R14" s="64"/>
-      <c r="S14" s="64"/>
-      <c r="T14" s="64"/>
-      <c r="U14" s="64"/>
-      <c r="V14" s="64"/>
-      <c r="W14" s="64"/>
-      <c r="X14" s="65"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="70"/>
+      <c r="X14" s="71"/>
       <c r="AM14" s="22"/>
       <c r="AO14" s="23"/>
     </row>
     <row r="15" spans="1:41" ht="19.95" customHeight="1">
       <c r="A15" s="22"/>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
-      <c r="S15" s="64"/>
-      <c r="T15" s="64"/>
-      <c r="U15" s="64"/>
-      <c r="V15" s="64"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="65"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
+      <c r="X15" s="71"/>
       <c r="AM15" s="22"/>
       <c r="AO15" s="23"/>
     </row>
     <row r="16" spans="1:41" ht="19.95" customHeight="1">
       <c r="A16" s="22"/>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="64"/>
-      <c r="O16" s="64"/>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="64"/>
-      <c r="R16" s="64"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="64"/>
-      <c r="U16" s="64"/>
-      <c r="V16" s="64"/>
-      <c r="W16" s="64"/>
-      <c r="X16" s="65"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="70"/>
+      <c r="X16" s="71"/>
       <c r="AM16" s="22"/>
       <c r="AO16" s="23"/>
     </row>
     <row r="17" spans="1:41" ht="19.95" customHeight="1">
       <c r="A17" s="22"/>
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
-      <c r="N17" s="64"/>
-      <c r="O17" s="64"/>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="64"/>
-      <c r="R17" s="64"/>
-      <c r="S17" s="64"/>
-      <c r="T17" s="64"/>
-      <c r="U17" s="64"/>
-      <c r="V17" s="64"/>
-      <c r="W17" s="64"/>
-      <c r="X17" s="65"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="71"/>
       <c r="AM17" s="22"/>
       <c r="AO17" s="23"/>
     </row>
     <row r="18" spans="1:41" ht="19.95" customHeight="1">
       <c r="A18" s="22"/>
-      <c r="D18" s="63" t="s">
+      <c r="D18" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="64"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="64"/>
-      <c r="R18" s="64"/>
-      <c r="S18" s="64"/>
-      <c r="T18" s="64"/>
-      <c r="U18" s="64"/>
-      <c r="V18" s="64"/>
-      <c r="W18" s="64"/>
-      <c r="X18" s="65"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
+      <c r="V18" s="70"/>
+      <c r="W18" s="70"/>
+      <c r="X18" s="71"/>
       <c r="AM18" s="22"/>
       <c r="AO18" s="23"/>
     </row>
     <row r="19" spans="1:41" ht="19.95" customHeight="1">
       <c r="A19" s="22"/>
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="64"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="64"/>
-      <c r="R19" s="64"/>
-      <c r="S19" s="64"/>
-      <c r="T19" s="64"/>
-      <c r="U19" s="64"/>
-      <c r="V19" s="64"/>
-      <c r="W19" s="64"/>
-      <c r="X19" s="65"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="70"/>
+      <c r="T19" s="70"/>
+      <c r="U19" s="70"/>
+      <c r="V19" s="70"/>
+      <c r="W19" s="70"/>
+      <c r="X19" s="71"/>
       <c r="AM19" s="22"/>
       <c r="AO19" s="23"/>
     </row>
     <row r="20" spans="1:41" ht="19.95" customHeight="1">
       <c r="A20" s="22"/>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="64"/>
-      <c r="R20" s="64"/>
-      <c r="S20" s="64"/>
-      <c r="T20" s="64"/>
-      <c r="U20" s="64"/>
-      <c r="V20" s="64"/>
-      <c r="W20" s="64"/>
-      <c r="X20" s="65"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="70"/>
+      <c r="U20" s="70"/>
+      <c r="V20" s="70"/>
+      <c r="W20" s="70"/>
+      <c r="X20" s="71"/>
       <c r="Y20" s="24"/>
       <c r="Z20" s="24"/>
       <c r="AA20" s="24"/>
@@ -5157,116 +5430,116 @@
     </row>
     <row r="21" spans="1:41" ht="19.95" customHeight="1">
       <c r="A21" s="22"/>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="64"/>
-      <c r="S21" s="64"/>
-      <c r="T21" s="64"/>
-      <c r="U21" s="64"/>
-      <c r="V21" s="64"/>
-      <c r="W21" s="64"/>
-      <c r="X21" s="65"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="70"/>
+      <c r="T21" s="70"/>
+      <c r="U21" s="70"/>
+      <c r="V21" s="70"/>
+      <c r="W21" s="70"/>
+      <c r="X21" s="71"/>
       <c r="AK21" s="24"/>
       <c r="AM21" s="22"/>
       <c r="AO21" s="23"/>
     </row>
     <row r="22" spans="1:41" ht="19.95" customHeight="1">
       <c r="A22" s="22"/>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="64"/>
-      <c r="U22" s="64"/>
-      <c r="V22" s="64"/>
-      <c r="W22" s="64"/>
-      <c r="X22" s="65"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="70"/>
+      <c r="T22" s="70"/>
+      <c r="U22" s="70"/>
+      <c r="V22" s="70"/>
+      <c r="W22" s="70"/>
+      <c r="X22" s="71"/>
       <c r="AK22" s="24"/>
       <c r="AM22" s="22"/>
       <c r="AO22" s="23"/>
     </row>
     <row r="23" spans="1:41" ht="19.95" customHeight="1">
       <c r="A23" s="22"/>
-      <c r="D23" s="63" t="s">
+      <c r="D23" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="64"/>
-      <c r="W23" s="64"/>
-      <c r="X23" s="65"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="70"/>
+      <c r="T23" s="70"/>
+      <c r="U23" s="70"/>
+      <c r="V23" s="70"/>
+      <c r="W23" s="70"/>
+      <c r="X23" s="71"/>
       <c r="AK23" s="24"/>
       <c r="AM23" s="22"/>
       <c r="AO23" s="23"/>
     </row>
     <row r="24" spans="1:41" ht="19.95" customHeight="1">
       <c r="A24" s="22"/>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="64"/>
-      <c r="R24" s="64"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="64"/>
-      <c r="U24" s="64"/>
-      <c r="V24" s="64"/>
-      <c r="W24" s="64"/>
-      <c r="X24" s="65"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
+      <c r="S24" s="70"/>
+      <c r="T24" s="70"/>
+      <c r="U24" s="70"/>
+      <c r="V24" s="70"/>
+      <c r="W24" s="70"/>
+      <c r="X24" s="71"/>
       <c r="AK24" s="24"/>
       <c r="AM24" s="22"/>
       <c r="AO24" s="23"/>
@@ -7121,29 +7394,6 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A1:N4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="AB1:AD2"/>
-    <mergeCell ref="AE1:AH2"/>
-    <mergeCell ref="T4:AA4"/>
-    <mergeCell ref="AM6:AO6"/>
-    <mergeCell ref="AL1:AO2"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="T3:AA3"/>
-    <mergeCell ref="AB3:AD4"/>
-    <mergeCell ref="AE3:AH4"/>
-    <mergeCell ref="AI3:AK4"/>
-    <mergeCell ref="AL3:AO4"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="AI1:AK2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="A6:AL6"/>
     <mergeCell ref="D23:X23"/>
     <mergeCell ref="D24:X24"/>
     <mergeCell ref="D9:X9"/>
@@ -7160,6 +7410,29 @@
     <mergeCell ref="D21:X21"/>
     <mergeCell ref="D22:X22"/>
     <mergeCell ref="D16:X16"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="A6:AL6"/>
+    <mergeCell ref="AM6:AO6"/>
+    <mergeCell ref="AL1:AO2"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="T3:AA3"/>
+    <mergeCell ref="AB3:AD4"/>
+    <mergeCell ref="AE3:AH4"/>
+    <mergeCell ref="AI3:AK4"/>
+    <mergeCell ref="AL3:AO4"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="AI1:AK2"/>
+    <mergeCell ref="A1:N4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="AB1:AD2"/>
+    <mergeCell ref="AE1:AH2"/>
+    <mergeCell ref="T4:AA4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
